--- a/static/changsha_houses.xlsx
+++ b/static/changsha_houses.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12375"/>
+    <workbookView windowWidth="30720" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5067,7 +5067,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J997"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
@@ -36984,7 +36984,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -36996,7 +36996,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
